--- a/data/trans_dic/P36$cafe-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$cafe-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,...</t>
+          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,06; 94,36</t>
+          <t>91,18; 94,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,72; 94,13</t>
+          <t>90,69; 94,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,13; 93,35</t>
+          <t>89,1; 93,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,07; 94,87</t>
+          <t>92,06; 94,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,08; 96,52</t>
+          <t>94,08; 96,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,61; 97,22</t>
+          <t>94,5; 97,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,31; 94,4</t>
+          <t>92,24; 94,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,11; 95,19</t>
+          <t>93,08; 95,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,93; 95,15</t>
+          <t>92,9; 95,04</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,52; 92,33</t>
+          <t>89,43; 92,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,6; 92,34</t>
+          <t>89,26; 92,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,33; 91,15</t>
+          <t>88,5; 91,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88,33; 91,33</t>
+          <t>88,36; 91,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,15; 92,84</t>
+          <t>90,1; 92,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,51; 93,87</t>
+          <t>91,31; 93,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,34; 91,49</t>
+          <t>89,33; 91,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,28; 92,2</t>
+          <t>90,34; 92,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90,2; 91,98</t>
+          <t>90,28; 92,06</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,73; 92,95</t>
+          <t>87,99; 92,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,51; 94,1</t>
+          <t>88,76; 94,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,48; 95,76</t>
+          <t>91,44; 95,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,76; 93,76</t>
+          <t>88,5; 93,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93,4; 97,29</t>
+          <t>93,47; 97,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,67; 94,87</t>
+          <t>90,28; 94,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,01; 92,7</t>
+          <t>89,05; 92,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,8; 95,05</t>
+          <t>91,72; 95,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,54; 94,75</t>
+          <t>91,68; 94,88</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,48; 92,43</t>
+          <t>90,33; 92,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,34; 92,39</t>
+          <t>90,4; 92,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,76; 91,8</t>
+          <t>89,66; 91,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,66; 92,53</t>
+          <t>90,53; 92,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,59; 94,37</t>
+          <t>92,55; 94,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,79; 94,35</t>
+          <t>92,76; 94,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,89; 92,16</t>
+          <t>90,79; 92,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,86; 93,23</t>
+          <t>91,89; 93,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,62; 92,9</t>
+          <t>91,58; 92,92</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,...</t>
+          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>935853; 969811</t>
+          <t>937117; 969262</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>882378; 915597</t>
+          <t>882054; 915238</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>670733; 702549</t>
+          <t>670548; 701934</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1208957; 1245822</t>
+          <t>1208892; 1245283</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1256652; 1289229</t>
+          <t>1256719; 1288499</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>939954; 965836</t>
+          <t>938833; 965222</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2160914; 2209713</t>
+          <t>2159286; 2207589</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2149405; 2197341</t>
+          <t>2148660; 2195213</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1622654; 1661284</t>
+          <t>1622079; 1659425</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1515109; 1562601</t>
+          <t>1513540; 1563711</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1757236; 1810917</t>
+          <t>1750540; 1808533</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1832143; 1890578</t>
+          <t>1835592; 1890382</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1400593; 1448199</t>
+          <t>1401031; 1447547</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1581981; 1629233</t>
+          <t>1581076; 1630485</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1817615; 1864567</t>
+          <t>1813551; 1861511</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2928490; 2999124</t>
+          <t>2928143; 2996431</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3354901; 3426260</t>
+          <t>3356886; 3429233</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3662714; 3734823</t>
+          <t>3665605; 3738188</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>482211; 510887</t>
+          <t>483607; 510235</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>424972; 451810</t>
+          <t>426190; 451697</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>500293; 523709</t>
+          <t>500073; 523686</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>422858; 446700</t>
+          <t>421618; 446049</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>427268; 445050</t>
+          <t>427606; 445066</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>497893; 520947</t>
+          <t>495742; 519599</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>913248; 951138</t>
+          <t>913680; 951878</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>860766; 891235</t>
+          <t>859939; 890880</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1003316; 1038504</t>
+          <t>1004856; 1039863</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2958647; 3022335</t>
+          <t>2953472; 3020686</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3084153; 3154136</t>
+          <t>3085992; 3156079</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3028317; 3097145</t>
+          <t>3024808; 3095560</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3060053; 3122923</t>
+          <t>3055452; 3122071</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3285065; 3348488</t>
+          <t>3283910; 3350093</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3274397; 3329634</t>
+          <t>3273370; 3329756</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6039320; 6124212</t>
+          <t>6033195; 6125749</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6395451; 6490695</t>
+          <t>6397560; 6493679</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6324201; 6412535</t>
+          <t>6321457; 6413685</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$cafe-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$cafe-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,18; 94,31</t>
+          <t>91,24; 94,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,69; 94,1</t>
+          <t>90,42; 93,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,1; 93,27</t>
+          <t>89,41; 93,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,06; 94,83</t>
+          <t>92,43; 94,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,08; 96,46</t>
+          <t>94,18; 96,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,5; 97,16</t>
+          <t>94,67; 97,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,24; 94,31</t>
+          <t>92,26; 94,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,08; 95,1</t>
+          <t>93,09; 95,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,9; 95,04</t>
+          <t>92,87; 95,18</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,43; 92,39</t>
+          <t>89,48; 92,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,26; 92,22</t>
+          <t>89,52; 92,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,5; 91,14</t>
+          <t>88,27; 91,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88,36; 91,29</t>
+          <t>88,36; 91,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,1; 92,91</t>
+          <t>90,24; 92,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,31; 93,72</t>
+          <t>91,44; 93,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,33; 91,41</t>
+          <t>89,37; 91,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,34; 92,28</t>
+          <t>90,24; 92,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90,28; 92,06</t>
+          <t>90,28; 92,04</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,99; 92,83</t>
+          <t>87,68; 92,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,76; 94,08</t>
+          <t>88,54; 93,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,44; 95,76</t>
+          <t>91,62; 95,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,5; 93,63</t>
+          <t>88,62; 94,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93,47; 97,29</t>
+          <t>93,33; 97,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,28; 94,62</t>
+          <t>90,36; 94,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,05; 92,77</t>
+          <t>89,02; 92,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,72; 95,02</t>
+          <t>91,71; 95,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,68; 94,88</t>
+          <t>91,63; 94,73</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,33; 92,38</t>
+          <t>90,49; 92,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,4; 92,45</t>
+          <t>90,37; 92,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,66; 91,76</t>
+          <t>89,84; 91,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,53; 92,5</t>
+          <t>90,57; 92,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,55; 94,42</t>
+          <t>92,76; 94,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,76; 94,36</t>
+          <t>92,8; 94,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,79; 92,19</t>
+          <t>90,89; 92,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,89; 93,27</t>
+          <t>91,86; 93,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,58; 92,92</t>
+          <t>91,6; 92,92</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>937117; 969262</t>
+          <t>937761; 970124</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>882054; 915238</t>
+          <t>879498; 913813</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>670548; 701934</t>
+          <t>672895; 702019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1208892; 1245283</t>
+          <t>1213710; 1247195</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1256719; 1288499</t>
+          <t>1258033; 1288402</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>938833; 965222</t>
+          <t>940490; 964971</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2159286; 2207589</t>
+          <t>2159800; 2208767</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2148660; 2195213</t>
+          <t>2148884; 2197783</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1622079; 1659425</t>
+          <t>1621603; 1661936</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1513540; 1563711</t>
+          <t>1514446; 1563602</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1750540; 1808533</t>
+          <t>1755552; 1810047</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1835592; 1890382</t>
+          <t>1830957; 1891514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1401031; 1447547</t>
+          <t>1400984; 1447157</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1581076; 1630485</t>
+          <t>1583595; 1630948</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1813551; 1861511</t>
+          <t>1816313; 1863340</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2928143; 2996431</t>
+          <t>2929578; 2995219</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3356886; 3429233</t>
+          <t>3353180; 3426093</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3665605; 3738188</t>
+          <t>3665778; 3737352</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>483607; 510235</t>
+          <t>481936; 510517</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>426190; 451697</t>
+          <t>425129; 450493</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>500073; 523686</t>
+          <t>501059; 524019</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>421618; 446049</t>
+          <t>422203; 447985</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>427606; 445066</t>
+          <t>426937; 445730</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>495742; 519599</t>
+          <t>496196; 520192</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>913680; 951878</t>
+          <t>913383; 951383</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>859939; 890880</t>
+          <t>859929; 891261</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1004856; 1039863</t>
+          <t>1004306; 1038263</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2953472; 3020686</t>
+          <t>2958997; 3023394</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3085992; 3156079</t>
+          <t>3085073; 3156255</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3024808; 3095560</t>
+          <t>3030833; 3098287</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3055452; 3122071</t>
+          <t>3056925; 3121659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3283910; 3350093</t>
+          <t>3291265; 3348060</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3273370; 3329756</t>
+          <t>3274730; 3334357</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6033195; 6125749</t>
+          <t>6039299; 6126045</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6397560; 6493679</t>
+          <t>6395189; 6488198</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6321457; 6413685</t>
+          <t>6323001; 6413524</t>
         </is>
       </c>
     </row>
